--- a/input/tneb-tests.xlsx
+++ b/input/tneb-tests.xlsx
@@ -28,7 +28,7 @@
     <t>ExpectedResult</t>
   </si>
   <si>
-    <t>TC-EB-001</t>
+    <t>TC-TNEB-001</t>
   </si>
   <si>
     <t>Download an e-Invoice</t>
@@ -91,7 +91,7 @@
     <t>Nothing was rejected</t>
   </si>
   <si>
-    <t>TC-EB-002</t>
+    <t>TC-TNEB-002</t>
   </si>
   <si>
     <t>The e-Invoice form is reachable without signing in</t>
@@ -127,7 +127,7 @@
     <t>Both download options are offered</t>
   </si>
   <si>
-    <t>TC-EB-003</t>
+    <t>TC-TNEB-003</t>
   </si>
   <si>
     <t>Malformed details return no invoice</t>

--- a/input/tneb-tests.xlsx
+++ b/input/tneb-tests.xlsx
@@ -49,13 +49,13 @@
     <t>The e-Invoice form is displayed</t>
   </si>
   <si>
-    <t>Enter "123456789012" in the Consumer No box</t>
+    <t>Enter "&lt;consumer no&gt;" in the Consumer No box</t>
   </si>
   <si>
     <t>The consumer number is entered</t>
   </si>
   <si>
-    <t>Enter "9000000000" in the Registered Mobile No box</t>
+    <t>Enter "&lt;mobile no&gt;" in the Registered Mobile No box</t>
   </si>
   <si>
     <t>The mobile number is entered</t>
@@ -79,7 +79,7 @@
     <t>The bill is shown</t>
   </si>
   <si>
-    <t>Verify that the invoice summary contains "123456789012"</t>
+    <t>Verify that the invoice summary contains "&lt;consumer no&gt;"</t>
   </si>
   <si>
     <t>The bill is for this consumer</t>
